--- a/Прогноз 2026 — Маркет и ОФД.xlsx
+++ b/Прогноз 2026 — Маркет и ОФД.xlsx
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>70592953.99377041</v>
+        <v>119039603</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>37544672.43728799</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>30266040.05853673</v>
+        <v>49034607</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>15306086.82974042</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>23919618.05</v>
+        <v>44473700</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>18897934.4</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.7903121123126023</v>
+        <v>0.906985957897042</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>1.234667920691555</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>-0.4232124223267739</v>
+        <v>-0.2083540165606678</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>-0.1571918488066785</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46046500.30052106</v>
+        <v>93076114.69332391</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>38625598.4183249</v>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>52188034.42302756</v>
+        <v>101995713.5958934</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>43317847.53680471</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>55808687.64919892</v>
+        <v>108426695.0560018</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>46488369.60313693</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.652281817029282</v>
+        <v>0.7818920119661682</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>1.028790395836917</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>0.7392810680175387</v>
+        <v>0.8568216881225098</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>1.153768157364</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.7905702267980435</v>
+        <v>0.9108455700747073</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>1.238214814120109</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>существенный недобор</t>
+          <t>недовыполнение</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>3763.720949736331</v>
+        <v>6399</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>7375.265327374596</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>1673.567250287371</v>
+        <v>2737</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>3008.397945204254</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1397</v>
+        <v>2458</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>3187</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.8347438680818585</v>
+        <v>0.8980635732553891</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>1.05936782900695</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>-0.4921846601235915</v>
+        <v>-0.3168426903835464</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>-0.2738664843928002</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>2413.898671262295</v>
+        <v>4749.035887506989</v>
       </c>
       <c r="C26" s="11" t="n">
         <v>5959.11800642271</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>2889.28020700411</v>
+        <v>5370.971244904632</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>7082.243156846213</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>3154.164532757862</v>
+        <v>5801.397388070602</v>
       </c>
       <c r="C28" s="11" t="n">
         <v>7813.118818211061</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.6413596288086666</v>
+        <v>0.7421528188009048</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>0.8079869322537312</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.7676658938294881</v>
+        <v>0.8393454047358389</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>0.9602696096314284</v>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.838044205423579</v>
+        <v>0.9066099996984844</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>1.05936782900695</v>
@@ -2028,7 +2028,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты Проект общий=Маркет · Афина · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Продукт = Маркет · Подключение · Онлайн (дашборд) · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -2076,13 +2076,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6263511.348942125</v>
+        <v>9780158</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8321032.01</v>
+        <v>10566339</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4200496.390000001</v>
+        <v>8241025</v>
       </c>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>6056422.316035671</v>
+        <v>9456800</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7282044.609999999</v>
+        <v>10162594</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4351111.290000001</v>
+        <v>9199025</v>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7033099.083469328</v>
+        <v>10981834</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8580171.789999999</v>
+        <v>11323288</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5962804.63</v>
+        <v>10261583</v>
       </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>6061387.442087491</v>
+        <v>10450826</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10007206.16</v>
+        <v>14129486</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4702395.83</v>
+        <v>8993089</v>
       </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4851619.868002112</v>
+        <v>8364989</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7279956.68</v>
+        <v>9997066</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4702809.91</v>
+        <v>7778978</v>
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
@@ -2171,20 +2171,20 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>5986082.105809628</v>
+        <v>10320988</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>8233697.189999999</v>
+        <v>11423141</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n">
-        <v>4682886.849717567</v>
+        <v>9101776.480453128</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4390375.319541274</v>
+        <v>8534558.684505247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4749094.257514948</v>
+        <v>9360991.187623875</v>
       </c>
     </row>
     <row r="11">
@@ -2194,20 +2194,20 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5872570.357098185</v>
+        <v>10125275</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7161253.78</v>
+        <v>9919931</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n">
-        <v>4241057.002101946</v>
+        <v>8417917.967619848</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3651095.14000004</v>
+        <v>7578916.400000003</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4641163.483622639</v>
+        <v>9183482.244845971</v>
       </c>
     </row>
     <row r="12">
@@ -2217,20 +2217,20 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5226458.227449151</v>
+        <v>9011271</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5821013.07</v>
+        <v>7919160</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>3538868.014024282</v>
+        <v>7203853.966861567</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2310854.430000043</v>
+        <v>5578145.400000005</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4130533.241648918</v>
+        <v>8344623.875908504</v>
       </c>
     </row>
     <row r="13">
@@ -2240,20 +2240,20 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>5096999.718052451</v>
+        <v>8788064</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>6738697.36</v>
+        <v>9186864</v>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n">
-        <v>3777359.995363969</v>
+        <v>7614401.594095069</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3228538.720000045</v>
+        <v>6845849.400000002</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4028220.613630771</v>
+        <v>8258569.730360099</v>
       </c>
     </row>
     <row r="14">
@@ -2263,20 +2263,20 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>5770038.007771566</v>
+        <v>9948492</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>6788530.22</v>
+        <v>8738891</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n">
-        <v>3971011.621105135</v>
+        <v>7845053.186182311</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3278371.580000049</v>
+        <v>6397876.400000004</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>4560130.926045946</v>
+        <v>9023142.546251059</v>
       </c>
     </row>
     <row r="15">
@@ -2286,20 +2286,20 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5630589.890397409</v>
+        <v>9708061</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5841716.4</v>
+        <v>7976369</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
-        <v>3564954.739386308</v>
+        <v>7443083.243262713</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2331557.760000055</v>
+        <v>5635354.400000005</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4449923.389845961</v>
+        <v>8805075.005407915</v>
       </c>
     </row>
     <row r="16">
@@ -2309,20 +2309,20 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>6744175.628655292</v>
+        <v>12102845</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>7617427.85</v>
+        <v>11983893</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
-        <v>4492278.151328357</v>
+        <v>9895927.157418748</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2936089.30097956</v>
+        <v>8031714.008818635</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5330003.686889737</v>
+        <v>10977110.46560442</v>
       </c>
     </row>
     <row r="17">
@@ -2332,20 +2332,20 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>70592953.99377041</v>
+        <v>119039603</v>
       </c>
       <c r="C17" s="13" t="n"/>
       <c r="D17" s="14" t="n">
-        <v>23919618.05</v>
+        <v>44473700</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>52188034.42302756</v>
+        <v>101995713.5958934</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>46046500.30052106</v>
+        <v>93076114.69332391</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>55808687.64919892</v>
+        <v>108426695.0560018</v>
       </c>
     </row>
   </sheetData>
@@ -2382,7 +2382,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты Проект общий=Маркет · Афина · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Продукт = Маркет · Подключение · Онлайн (дашборд) · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>391.0186810286141</v>
+        <v>617</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>579</v>
+        <v>752</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>246</v>
+        <v>477</v>
       </c>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="11" t="n"/>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>337.0446834506792</v>
+        <v>532</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>484</v>
+        <v>644</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>260</v>
+        <v>501</v>
       </c>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="11" t="n"/>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>380.2864858600663</v>
+        <v>600</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>565</v>
+        <v>706</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>376</v>
+        <v>600</v>
       </c>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>329.6340999740057</v>
+        <v>576</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>663</v>
+        <v>883</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>279</v>
+        <v>477</v>
       </c>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="11" t="n"/>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>235.5832999740057</v>
+        <v>412</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>460</v>
+        <v>613</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
@@ -2525,20 +2525,20 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>300.8522999740057</v>
+        <v>526</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>519</v>
+        <v>700</v>
       </c>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n">
-        <v>251.7259962384995</v>
+        <v>472.1624872282246</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>238.2874056592341</v>
+        <v>461.7158815494085</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>263.5561613958561</v>
+        <v>478.2101167315175</v>
       </c>
     </row>
     <row r="11">
@@ -2548,20 +2548,20 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>321.5809999740057</v>
+        <v>562</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>454</v>
+        <v>584</v>
       </c>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n">
-        <v>234.4429835212009</v>
+        <v>440.9630121903972</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>183.2000000000015</v>
+        <v>356.0000000000001</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>268.4377678199336</v>
+        <v>504.7117281695287</v>
       </c>
     </row>
     <row r="12">
@@ -2571,20 +2571,20 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>261.8799997894656</v>
+        <v>458</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n">
-        <v>181.1647451861427</v>
+        <v>355.8579974503227</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>90.20000000000175</v>
+        <v>230.0000000000003</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>218.6027239975348</v>
+        <v>447.4082591923428</v>
       </c>
     </row>
     <row r="13">
@@ -2594,20 +2594,20 @@
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>272.6975998761206</v>
+        <v>477</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n">
-        <v>196.2398574774597</v>
+        <v>383.6197751567994</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>134.2000000000018</v>
+        <v>288.9999999999999</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>227.6326493372319</v>
+        <v>441.14108741163</v>
       </c>
     </row>
     <row r="14">
@@ -2617,20 +2617,20 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>319.9106998873506</v>
+        <v>559</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>438</v>
+        <v>529</v>
       </c>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n">
-        <v>219.8854598721577</v>
+        <v>416.6644812727669</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>160.1485475319592</v>
+        <v>301.0000000000001</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>267.0434950647416</v>
+        <v>502.0175374497625</v>
       </c>
     </row>
     <row r="15">
@@ -2640,20 +2640,20 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>279.9652999740057</v>
+        <v>489</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>360</v>
+        <v>456</v>
       </c>
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n">
-        <v>178.1517183022359</v>
+        <v>363.6620446519421</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>89.20000000000215</v>
+        <v>228.0000000000002</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>233.6993174289994</v>
+        <v>439.1530873218853</v>
       </c>
     </row>
     <row r="16">
@@ -2663,20 +2663,20 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>333.2667999740057</v>
+        <v>591</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>475</v>
+        <v>673</v>
       </c>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n">
-        <v>230.669446406414</v>
+        <v>480.0414469541792</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>121.662718071095</v>
+        <v>425.3200059575791</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>278.1924177135646</v>
+        <v>530.7555717939349</v>
       </c>
     </row>
     <row r="17">
@@ -2686,20 +2686,20 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>3763.720949736331</v>
+        <v>6399</v>
       </c>
       <c r="C17" s="13" t="n"/>
       <c r="D17" s="15" t="n">
-        <v>1397</v>
+        <v>2458</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>2889.28020700411</v>
+        <v>5370.971244904632</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2413.898671262295</v>
+        <v>4749.035887506989</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>3154.164532757862</v>
+        <v>5801.397388070602</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2736,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты Проект п453 · Афина · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты Проект п453 · Афина · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>55790466.58520305</v>
+        <v>107967248.3546386</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>46355202.65119191</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>51722126.59464855</v>
+        <v>97631341.61583415</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>40564908.19614005</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>49540983.0152276</v>
+        <v>102360063.267196</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>44668260.26461965</v>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>47550843.44000033</v>
+        <v>95234846.80000003</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>39671501.93799989</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>52188034.42302756</v>
+        <v>101995713.5958934</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>43317847.53680471</v>
@@ -4517,40 +4517,40 @@
         <v>2026</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>6263511</v>
+        <v>9780158</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>6056422</v>
+        <v>9456800</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>7033099</v>
+        <v>10981834</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>6061387</v>
+        <v>10450826</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>4851620</v>
+        <v>8364989</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>5986082</v>
+        <v>10320988</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>5872570</v>
+        <v>10125275</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>5226458</v>
+        <v>9011271</v>
       </c>
       <c r="L4" s="20" t="n">
-        <v>5097000</v>
+        <v>8788064</v>
       </c>
       <c r="M4" s="20" t="n">
-        <v>5770038</v>
+        <v>9948492</v>
       </c>
       <c r="N4" s="20" t="n">
-        <v>5630590</v>
+        <v>9708061</v>
       </c>
       <c r="O4" s="20" t="n">
-        <v>6744176</v>
+        <v>12102845</v>
       </c>
     </row>
     <row r="5">
@@ -4568,40 +4568,40 @@
         <v>2025</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>8321032</v>
+        <v>10566339</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>7282045</v>
+        <v>10162594</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>8580172</v>
+        <v>11323288</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>10007206</v>
+        <v>14129486</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>7279957</v>
+        <v>9997066</v>
       </c>
       <c r="I5" s="20" t="n">
-        <v>8233697</v>
+        <v>11423141</v>
       </c>
       <c r="J5" s="20" t="n">
-        <v>7161254</v>
+        <v>9919931</v>
       </c>
       <c r="K5" s="20" t="n">
-        <v>5821013</v>
+        <v>7919160</v>
       </c>
       <c r="L5" s="20" t="n">
-        <v>6738697</v>
+        <v>9186864</v>
       </c>
       <c r="M5" s="20" t="n">
-        <v>6788530</v>
+        <v>8738891</v>
       </c>
       <c r="N5" s="20" t="n">
-        <v>5841716</v>
+        <v>7976369</v>
       </c>
       <c r="O5" s="20" t="n">
-        <v>7617428</v>
+        <v>11983893</v>
       </c>
     </row>
     <row r="6">
@@ -4619,22 +4619,22 @@
         <v>2026</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>4200496</v>
+        <v>8241025</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>4351111</v>
+        <v>9199025</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>5962805</v>
+        <v>10261583</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>4702396</v>
+        <v>8993089</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>4702810</v>
+        <v>7778978</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>1831026</v>
+        <v>3207489</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>0</v>
